--- a/resources/topic/银行从业中级银行管理_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业中级银行管理_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R0bd8a84220c748dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R43d81fc6edd8459d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R6443a121315d4544"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R00e11d4b9c544de0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R657bdbefb568495f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Ra05688c287994419"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -65453,7 +65453,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-10 09:14:07+08:00（本地时间）</x:v>
+        <x:v>2026-09-10 15:11:30+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -65477,7 +65477,7 @@
         <x:v>说明</x:v>
       </x:c>
       <x:c r="B8" s="13" t="str">
-        <x:v>权限不足/收费题已保留行并标注；案例材料题已展开为独立题目，材料文本放在题目前。 本次对 1 道仅解析含图的题目执行 OCR，成功 1 道，失败 0 道；失败题保留图片地址并进入拒绝清单。</x:v>
+        <x:v>权限不足/收费题已保留行并标注；案例材料题已展开为独立题目，材料文本放在题目前。 复用可信 Excel 中 1 道解析图片的既有文字；仅在来源题目 ID、题干、选项和答案均一致时复用。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/resources/topic/银行从业中级银行管理_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业中级银行管理_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R00e11d4b9c544de0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R657bdbefb568495f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Ra05688c287994419"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Rfa7b18a037fa4858"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="Ra8d621d35afb438f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R63f44950d98948db"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -65453,7 +65453,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-10 15:11:30+08:00（本地时间）</x:v>
+        <x:v>2026-09-12 01:06:04+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
